--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486756_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486756_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.1506</v>
+        <v>6.7038</v>
       </c>
       <c r="E2" t="n">
-        <v>7.2183</v>
+        <v>6.9702</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.0677</v>
+        <v>-0.2664</v>
       </c>
       <c r="G2" t="n">
         <v>5.9272</v>
@@ -610,13 +610,13 @@
         <v>2.51</v>
       </c>
       <c r="S2" t="n">
-        <v>2.0191</v>
+        <v>1.5723</v>
       </c>
       <c r="T2" t="n">
-        <v>1.2682</v>
+        <v>1.0201</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7508</v>
+        <v>0.5522</v>
       </c>
       <c r="V2" t="n">
         <v>0.9421</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.8463</v>
+        <v>2.2876</v>
       </c>
       <c r="E3" t="n">
-        <v>2.274</v>
+        <v>2.5912</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.4278</v>
+        <v>-0.3036</v>
       </c>
       <c r="G3" t="n">
         <v>0.059</v>
@@ -688,13 +688,13 @@
         <v>2.51</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7446</v>
+        <v>1.186</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4684</v>
+        <v>0.7856</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2762</v>
+        <v>0.4004</v>
       </c>
       <c r="V3" t="n">
         <v>0.6565</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3721</v>
+        <v>1.5625</v>
       </c>
       <c r="E4" t="n">
-        <v>2.3457</v>
+        <v>2.5113</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.9736</v>
+        <v>-0.9488</v>
       </c>
       <c r="G4" t="n">
         <v>0.7445000000000001</v>
@@ -766,13 +766,13 @@
         <v>1.7377</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0717</v>
+        <v>0.2621</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0004</v>
+        <v>0.1652</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0721</v>
+        <v>0.0969</v>
       </c>
       <c r="V4" t="n">
         <v>0.9421</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. THIAW</t>
+          <t>A. LOPEZ ROMERA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0298</v>
+        <v>-0.7422</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6227</v>
+        <v>0.6993</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.6525</v>
+        <v>-1.4415</v>
       </c>
       <c r="G5" t="n">
-        <v>-4.5873</v>
+        <v>0.2442</v>
       </c>
       <c r="H5" t="n">
-        <v>-4.4335</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1538</v>
+        <v>0.2442</v>
       </c>
       <c r="J5" t="n">
-        <v>-2.779</v>
+        <v>0.6511</v>
       </c>
       <c r="K5" t="n">
-        <v>-3.6742</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8952</v>
+        <v>0.6511</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.8083</v>
+        <v>-0.4069</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.7593</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.049</v>
+        <v>-0.4069</v>
       </c>
       <c r="P5" t="n">
-        <v>2.1239</v>
+        <v>0.1931</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.3862</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.51</v>
+        <v>0.1931</v>
       </c>
       <c r="S5" t="n">
-        <v>4.2752</v>
+        <v>0.0482</v>
       </c>
       <c r="T5" t="n">
-        <v>3.5022</v>
+        <v>0.0482</v>
       </c>
       <c r="U5" t="n">
-        <v>0.773</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.8415</v>
+        <v>-1.2277</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2856</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.1271</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.7153</v>
+        <v>-0.8146</v>
       </c>
       <c r="E6" t="n">
         <v>0.0064</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.7216</v>
+        <v>-0.821</v>
       </c>
       <c r="G6" t="n">
         <v>-1.449</v>
@@ -922,13 +922,13 @@
         <v>0.5792</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1545</v>
+        <v>0.0552</v>
       </c>
       <c r="T6" t="n">
         <v>0.2206</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.06610000000000001</v>
+        <v>-0.1654</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. LOPEZ ROMERA</t>
+          <t>L. BULASHVILI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.8456</v>
+        <v>-2.0644</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5959</v>
+        <v>-0.863</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.4415</v>
+        <v>-1.2014</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2442</v>
+        <v>-4.6326</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>-0.1793</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2442</v>
+        <v>-4.4534</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6511</v>
+        <v>-0.7002</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1.4766</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6511</v>
+        <v>-2.1768</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.4069</v>
+        <v>-3.9324</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>-1.6558</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.4069</v>
+        <v>-2.2766</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1931</v>
+        <v>0.9654</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-2.1239</v>
       </c>
       <c r="R7" t="n">
-        <v>0.1931</v>
+        <v>3.0892</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0552</v>
+        <v>0.0896</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0552</v>
+        <v>0.4478</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>-0.3582</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.2277</v>
+        <v>1.5133</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.5133</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2277</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. CAULIN TORNERO</t>
+          <t>I. KANE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.1404</v>
+        <v>-2.185</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2846</v>
+        <v>-1.4089</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.8558</v>
+        <v>-0.776</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.5844</v>
+        <v>-0.5478</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.1376</v>
+        <v>-0.4483</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.4468</v>
+        <v>-0.09950000000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.2666</v>
+        <v>1.3496</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3799</v>
+        <v>0.6555</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6465</v>
+        <v>0.6941000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.3178</v>
+        <v>-1.8973</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.5175</v>
+        <v>-1.1038</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.8003</v>
+        <v>-0.7935</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9654</v>
+        <v>-2.1239</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.1931</v>
+        <v>-3.2823</v>
       </c>
       <c r="R8" t="n">
         <v>1.1585</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5793</v>
+        <v>0.7723</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1105</v>
+        <v>0.5238</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4688</v>
+        <v>0.2484</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.9421</v>
+        <v>-0.2856</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2856</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.2277</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>I. KANE</t>
+          <t>M. THIAW</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.2165</v>
+        <v>-2.2569</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.2915</v>
+        <v>-1.232</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.925</v>
+        <v>-1.025</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.5478</v>
+        <v>-4.5873</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.4483</v>
+        <v>-4.4335</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.09950000000000001</v>
+        <v>-0.1538</v>
       </c>
       <c r="J9" t="n">
-        <v>1.3496</v>
+        <v>-2.779</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6555</v>
+        <v>-3.6742</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6941000000000001</v>
+        <v>0.8952</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.8973</v>
+        <v>-1.8083</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.1038</v>
+        <v>-0.7593</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.7935</v>
+        <v>-1.049</v>
       </c>
       <c r="P9" t="n">
-        <v>-2.1239</v>
+        <v>2.1239</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.2823</v>
+        <v>-0.3862</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1585</v>
+        <v>2.51</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2593</v>
+        <v>2.0481</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3587</v>
+        <v>1.6476</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0994</v>
+        <v>0.4005</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.2856</v>
+        <v>-1.8415</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.2856</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.2856</v>
+        <v>-2.1271</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>L. BULASHVILI</t>
+          <t>A. CAULIN TORNERO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.5607</v>
+        <v>-2.8024</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.111</v>
+        <v>-0.0708</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.4497</v>
+        <v>-2.7317</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.6326</v>
+        <v>-2.5844</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.1793</v>
+        <v>-1.1376</v>
       </c>
       <c r="I10" t="n">
-        <v>-4.4534</v>
+        <v>-1.4468</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.7002</v>
+        <v>-0.2666</v>
       </c>
       <c r="K10" t="n">
-        <v>1.4766</v>
+        <v>0.3799</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.1768</v>
+        <v>-0.6465</v>
       </c>
       <c r="M10" t="n">
-        <v>-3.9324</v>
+        <v>-2.3178</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.6558</v>
+        <v>-1.5175</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.2766</v>
+        <v>-0.8003</v>
       </c>
       <c r="P10" t="n">
         <v>0.9654</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.1239</v>
+        <v>-0.1931</v>
       </c>
       <c r="R10" t="n">
-        <v>3.0892</v>
+        <v>1.1585</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.4067</v>
+        <v>-0.2413</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8002</v>
+        <v>0.1033</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6065</v>
+        <v>-0.3447</v>
       </c>
       <c r="V10" t="n">
-        <v>1.5133</v>
+        <v>-0.9421</v>
       </c>
       <c r="W10" t="n">
-        <v>1.5133</v>
+        <v>0.2856</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.1393</v>
+        <v>-0.3115999999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>8.375899999999998</v>
+        <v>9.2037</v>
       </c>
       <c r="F11" t="n">
-        <v>-9.5152</v>
+        <v>-9.5154</v>
       </c>
       <c r="G11" t="n">
         <v>-6.8262</v>
@@ -1288,7 +1288,7 @@
         <v>14.1825</v>
       </c>
       <c r="K11" t="n">
-        <v>6.213200000000001</v>
+        <v>6.2132</v>
       </c>
       <c r="L11" t="n">
         <v>7.9693</v>
@@ -1300,7 +1300,7 @@
         <v>-11.0387</v>
       </c>
       <c r="O11" t="n">
-        <v>-9.970000000000001</v>
+        <v>-9.969999999999999</v>
       </c>
       <c r="P11" t="n">
         <v>0.9653999999999998</v>
@@ -1312,16 +1312,16 @@
         <v>15.4462</v>
       </c>
       <c r="S11" t="n">
-        <v>4.9646</v>
+        <v>5.7925</v>
       </c>
       <c r="T11" t="n">
-        <v>4.1344</v>
+        <v>4.9622</v>
       </c>
       <c r="U11" t="n">
         <v>0.8301000000000001</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.2428999999999997</v>
+        <v>-0.2428999999999998</v>
       </c>
       <c r="W11" t="n">
         <v>4.5399</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>3.3273</v>
+        <v>3.4074</v>
       </c>
       <c r="E12" t="n">
-        <v>2.5596</v>
+        <v>2.3528</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7677</v>
+        <v>1.0546</v>
       </c>
       <c r="G12" t="n">
         <v>2.2805</v>
@@ -1390,13 +1390,13 @@
         <v>0.9654</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0112</v>
+        <v>0.0689</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1377</v>
+        <v>-0.0692</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1488</v>
+        <v>0.1381</v>
       </c>
       <c r="V12" t="n">
         <v>0.2856</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.7413</v>
+        <v>2.6806</v>
       </c>
       <c r="E13" t="n">
         <v>4.2185</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.4771</v>
+        <v>-1.5379</v>
       </c>
       <c r="G13" t="n">
         <v>0.5274</v>
@@ -1468,13 +1468,13 @@
         <v>2.1239</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.8218</v>
+        <v>-0.8826000000000001</v>
       </c>
       <c r="T13" t="n">
         <v>-0.0555</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.7663</v>
+        <v>-0.827</v>
       </c>
       <c r="V13" t="n">
         <v>1.1049</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.5159</v>
+        <v>2.2194</v>
       </c>
       <c r="E14" t="n">
-        <v>2.3537</v>
+        <v>2.0435</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1622</v>
+        <v>0.1759</v>
       </c>
       <c r="G14" t="n">
         <v>0.861</v>
@@ -1546,13 +1546,13 @@
         <v>1.1585</v>
       </c>
       <c r="S14" t="n">
-        <v>0.6895</v>
+        <v>0.393</v>
       </c>
       <c r="T14" t="n">
-        <v>0.248</v>
+        <v>-0.0622</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4415</v>
+        <v>0.4553</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.9063</v>
+        <v>1.9119</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.6012</v>
       </c>
       <c r="F15" t="n">
-        <v>1.0983</v>
+        <v>1.3107</v>
       </c>
       <c r="G15" t="n">
         <v>1.0893</v>
@@ -1624,13 +1624,13 @@
         <v>2.1239</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.9709</v>
+        <v>-0.9654</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1659</v>
+        <v>-0.3727</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.805</v>
+        <v>-0.5926</v>
       </c>
       <c r="V15" t="n">
         <v>2.9465</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. SOLA IDRISU</t>
+          <t>D. SANCHEZ PEREZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.0886</v>
+        <v>1.2498</v>
       </c>
       <c r="E16" t="n">
-        <v>1.2568</v>
+        <v>-0.0612</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.1682</v>
+        <v>1.311</v>
       </c>
       <c r="G16" t="n">
-        <v>3.1672</v>
+        <v>1.2138</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.0558</v>
+        <v>2.1656</v>
       </c>
       <c r="I16" t="n">
-        <v>4.2229</v>
+        <v>-0.9517</v>
       </c>
       <c r="J16" t="n">
-        <v>3.817</v>
+        <v>1.394</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.1927</v>
+        <v>1.9591</v>
       </c>
       <c r="L16" t="n">
-        <v>5.0097</v>
+        <v>-0.5651</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.6498</v>
+        <v>-0.1802</v>
       </c>
       <c r="N16" t="n">
-        <v>0.137</v>
+        <v>0.2065</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.7868000000000001</v>
+        <v>-0.3866</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>0.1931</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.3169</v>
+        <v>-1.3515</v>
       </c>
       <c r="R16" t="n">
-        <v>2.3169</v>
+        <v>1.5446</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.0716</v>
+        <v>-0.0344</v>
       </c>
       <c r="T16" t="n">
-        <v>0.4132</v>
+        <v>-0.1037</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4848</v>
+        <v>0.0693</v>
       </c>
       <c r="V16" t="n">
-        <v>-2.0069</v>
+        <v>-0.1228</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.6565</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.3505</v>
+        <v>-0.1228</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. SANCHEZ PEREZ</t>
+          <t>M. SOLA IDRISU</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8761</v>
+        <v>0.5742</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.3715</v>
+        <v>0.7397</v>
       </c>
       <c r="F17" t="n">
-        <v>1.2476</v>
+        <v>-0.1655</v>
       </c>
       <c r="G17" t="n">
-        <v>1.2138</v>
+        <v>3.1672</v>
       </c>
       <c r="H17" t="n">
-        <v>2.1656</v>
+        <v>-1.0558</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.9517</v>
+        <v>4.2229</v>
       </c>
       <c r="J17" t="n">
-        <v>1.394</v>
+        <v>3.817</v>
       </c>
       <c r="K17" t="n">
-        <v>1.9591</v>
+        <v>-1.1927</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.5651</v>
+        <v>5.0097</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.1802</v>
+        <v>-0.6498</v>
       </c>
       <c r="N17" t="n">
-        <v>0.2065</v>
+        <v>0.137</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.3866</v>
+        <v>-0.7868000000000001</v>
       </c>
       <c r="P17" t="n">
-        <v>0.1931</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.3515</v>
+        <v>-2.3169</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5446</v>
+        <v>2.3169</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4081</v>
+        <v>-0.5861</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4139</v>
+        <v>-0.1039</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0059</v>
+        <v>-0.4822</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.1228</v>
+        <v>-2.0069</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>-0.6565</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1228</v>
+        <v>-1.3505</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.009599999999999999</v>
+        <v>0.298</v>
       </c>
       <c r="E18" t="n">
-        <v>3.0386</v>
+        <v>2.9351</v>
       </c>
       <c r="F18" t="n">
-        <v>-3.0482</v>
+        <v>-2.6372</v>
       </c>
       <c r="G18" t="n">
         <v>2.1696</v>
@@ -1858,13 +1858,13 @@
         <v>1.5446</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.5005</v>
+        <v>-1.1929</v>
       </c>
       <c r="T18" t="n">
-        <v>0.11</v>
+        <v>0.0066</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.6105</v>
+        <v>-1.1995</v>
       </c>
       <c r="V18" t="n">
         <v>-1.0648</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.5232</v>
+        <v>-1.9965</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.4369</v>
+        <v>-0.0232</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.0863</v>
+        <v>-1.9733</v>
       </c>
       <c r="G19" t="n">
         <v>-1.9826</v>
@@ -1936,13 +1936,13 @@
         <v>1.1585</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7337</v>
+        <v>-0.2069</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4966</v>
+        <v>-0.083</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.237</v>
+        <v>-0.124</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.3877</v>
+        <v>-3.0815</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.0948</v>
+        <v>-1.8879</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.2929</v>
+        <v>-1.1936</v>
       </c>
       <c r="G20" t="n">
         <v>0.1318</v>
@@ -2014,13 +2014,13 @@
         <v>0.7723</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4303</v>
+        <v>-0.1241</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2759</v>
+        <v>-0.06909999999999999</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1544</v>
+        <v>-0.0551</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.3957</v>
+        <v>-4.7448</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.8168</v>
+        <v>-1.4031</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.5789</v>
+        <v>-3.3417</v>
       </c>
       <c r="G21" t="n">
         <v>-2.6317</v>
@@ -2092,13 +2092,13 @@
         <v>0.7723</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7060999999999999</v>
+        <v>-0.0552</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3311</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.375</v>
+        <v>-0.1378</v>
       </c>
       <c r="V21" t="n">
         <v>-0.8995</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>1.1393</v>
+        <v>2.518500000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>9.5152</v>
+        <v>9.5154</v>
       </c>
       <c r="F22" t="n">
-        <v>-8.375799999999998</v>
+        <v>-6.997</v>
       </c>
       <c r="G22" t="n">
         <v>6.8263</v>
@@ -2170,13 +2170,13 @@
         <v>14.4809</v>
       </c>
       <c r="S22" t="n">
-        <v>-4.9647</v>
+        <v>-3.585700000000001</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.83</v>
+        <v>-0.8301000000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>-4.134399999999999</v>
+        <v>-2.7555</v>
       </c>
       <c r="V22" t="n">
         <v>0.2430000000000001</v>
